--- a/config/Config/Data/人物&怪物.xlsx
+++ b/config/Config/Data/人物&怪物.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="194">
   <si>
     <t>##var</t>
   </si>
@@ -361,6 +361,15 @@
     <t>tm_junjun_inspect</t>
   </si>
   <si>
+    <t>TM_PaoPao</t>
+  </si>
+  <si>
+    <t>炮炮</t>
+  </si>
+  <si>
+    <t>土木圣体，搞钱大师，商务经理</t>
+  </si>
+  <si>
     <t>TM_wantao</t>
   </si>
   <si>
@@ -557,6 +566,15 @@
   </si>
   <si>
     <t>mow_eng_crush</t>
+  </si>
+  <si>
+    <t>temp_old</t>
+  </si>
+  <si>
+    <t>热心市民</t>
+  </si>
+  <si>
+    <t>仁心老陈有事，就是他们有事，真上。</t>
   </si>
   <si>
     <t>temp_hire</t>
@@ -951,7 +969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U30"/>
+  <dimension ref="A1:U32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13.571428571428571" customWidth="1"/>
@@ -1630,7 +1648,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>116</v>
       </c>
@@ -1640,137 +1658,86 @@
       <c r="D16" t="s">
         <v>118</v>
       </c>
-      <c r="E16" t="s">
+    </row>
+    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C17" t="s">
+        <v>120</v>
+      </c>
+      <c r="D17" t="s">
+        <v>121</v>
+      </c>
+      <c r="E17" t="s">
         <v>57</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F17" t="s">
         <v>58</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G17" t="s">
         <v>59</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H17" t="s">
         <v>60</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I17" t="s">
         <v>106</v>
       </c>
-      <c r="J16" t="s">
-        <v>119</v>
-      </c>
-      <c r="K16" t="s">
-        <v>120</v>
-      </c>
-      <c r="L16">
+      <c r="J17" t="s">
+        <v>122</v>
+      </c>
+      <c r="K17" t="s">
+        <v>123</v>
+      </c>
+      <c r="L17">
         <v>135</v>
       </c>
-      <c r="M16">
+      <c r="M17">
         <v>12</v>
       </c>
-      <c r="N16">
+      <c r="N17">
         <v>2.35</v>
       </c>
-      <c r="O16" t="s">
-        <v>121</v>
-      </c>
-      <c r="P16" t="s">
+      <c r="O17" t="s">
+        <v>124</v>
+      </c>
+      <c r="P17" t="s">
         <v>74</v>
       </c>
-      <c r="Q16">
+      <c r="Q17">
         <v>41</v>
       </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
         <v>1.5</v>
       </c>
-      <c r="U16">
+      <c r="U17">
         <v>0.4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>32</v>
       </c>
-      <c r="B17" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>123</v>
-      </c>
-      <c r="C18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D18" t="s">
         <v>125</v>
-      </c>
-      <c r="E18" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" t="s">
-        <v>58</v>
-      </c>
-      <c r="G18" t="s">
-        <v>59</v>
-      </c>
-      <c r="H18" t="s">
-        <v>89</v>
-      </c>
-      <c r="I18" t="s">
-        <v>126</v>
-      </c>
-      <c r="J18" t="s">
-        <v>127</v>
-      </c>
-      <c r="K18" t="s">
-        <v>128</v>
-      </c>
-      <c r="L18">
-        <v>100</v>
-      </c>
-      <c r="M18">
-        <v>12</v>
-      </c>
-      <c r="N18">
-        <v>2.5</v>
-      </c>
-      <c r="O18" t="s">
-        <v>129</v>
-      </c>
-      <c r="P18" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q18">
-        <v>30</v>
-      </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>1.5</v>
-      </c>
-      <c r="U18">
-        <v>0.4</v>
       </c>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C19" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D19" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E19" t="s">
         <v>57</v>
@@ -1785,31 +1752,31 @@
         <v>89</v>
       </c>
       <c r="I19" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J19" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K19" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="L19">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="M19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N19">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O19" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="P19" t="s">
         <v>74</v>
       </c>
       <c r="Q19">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -1824,194 +1791,194 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>133</v>
+      </c>
+      <c r="C20" t="s">
+        <v>134</v>
+      </c>
+      <c r="D20" t="s">
+        <v>135</v>
+      </c>
+      <c r="E20" t="s">
+        <v>57</v>
+      </c>
+      <c r="F20" t="s">
+        <v>58</v>
+      </c>
+      <c r="G20" t="s">
+        <v>59</v>
+      </c>
+      <c r="H20" t="s">
+        <v>89</v>
+      </c>
+      <c r="I20" t="s">
+        <v>129</v>
+      </c>
+      <c r="J20" t="s">
+        <v>136</v>
+      </c>
+      <c r="K20" t="s">
+        <v>137</v>
+      </c>
+      <c r="L20">
+        <v>105</v>
+      </c>
+      <c r="M20">
+        <v>11</v>
+      </c>
+      <c r="N20">
+        <v>2.45</v>
+      </c>
+      <c r="O20" t="s">
+        <v>138</v>
+      </c>
+      <c r="P20" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q20">
+        <v>50</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>1.5</v>
+      </c>
+      <c r="U20">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>32</v>
       </c>
-      <c r="B20" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>137</v>
-      </c>
-      <c r="C21" t="s">
-        <v>138</v>
-      </c>
-      <c r="D21" t="s">
         <v>139</v>
       </c>
-      <c r="E21" t="s">
+    </row>
+    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>140</v>
+      </c>
+      <c r="C22" t="s">
+        <v>141</v>
+      </c>
+      <c r="D22" t="s">
+        <v>142</v>
+      </c>
+      <c r="E22" t="s">
         <v>57</v>
       </c>
-      <c r="F21" t="s">
-        <v>140</v>
-      </c>
-      <c r="G21" t="s">
+      <c r="F22" t="s">
+        <v>143</v>
+      </c>
+      <c r="G22" t="s">
         <v>70</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H22" t="s">
         <v>60</v>
       </c>
-      <c r="I21" t="s">
-        <v>141</v>
-      </c>
-      <c r="J21" t="s">
-        <v>142</v>
-      </c>
-      <c r="K21" t="s">
-        <v>143</v>
-      </c>
-      <c r="L21">
+      <c r="I22" t="s">
+        <v>144</v>
+      </c>
+      <c r="J22" t="s">
+        <v>145</v>
+      </c>
+      <c r="K22" t="s">
+        <v>146</v>
+      </c>
+      <c r="L22">
         <v>95</v>
       </c>
-      <c r="M21">
+      <c r="M22">
         <v>16</v>
       </c>
-      <c r="N21">
+      <c r="N22">
         <v>2.4</v>
       </c>
-      <c r="O21" t="s">
-        <v>144</v>
-      </c>
-      <c r="P21" t="s">
+      <c r="O22" t="s">
+        <v>147</v>
+      </c>
+      <c r="P22" t="s">
         <v>74</v>
       </c>
-      <c r="Q21">
+      <c r="Q22">
         <v>10</v>
       </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
         <v>1.5</v>
       </c>
-      <c r="U21">
+      <c r="U22">
         <v>0.4</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>32</v>
       </c>
-      <c r="B22" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>146</v>
-      </c>
-      <c r="C23" t="s">
-        <v>147</v>
-      </c>
-      <c r="D23" t="s">
         <v>148</v>
-      </c>
-      <c r="E23" t="s">
-        <v>57</v>
-      </c>
-      <c r="F23" t="s">
-        <v>58</v>
-      </c>
-      <c r="G23" t="s">
-        <v>59</v>
-      </c>
-      <c r="H23" t="s">
-        <v>60</v>
-      </c>
-      <c r="I23" t="s">
-        <v>149</v>
-      </c>
-      <c r="J23" t="s">
-        <v>150</v>
-      </c>
-      <c r="K23" t="s">
-        <v>151</v>
-      </c>
-      <c r="L23">
-        <v>145</v>
-      </c>
-      <c r="M23">
-        <v>10.5</v>
-      </c>
-      <c r="N23">
-        <v>2.15</v>
-      </c>
-      <c r="O23" t="s">
-        <v>152</v>
-      </c>
-      <c r="P23" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q23">
-        <v>12</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>1.5</v>
-      </c>
-      <c r="U23">
-        <v>0.4</v>
       </c>
     </row>
     <row r="24" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C24" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D24" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E24" t="s">
         <v>57</v>
       </c>
       <c r="F24" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="G24" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="H24" t="s">
         <v>60</v>
       </c>
       <c r="I24" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J24" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="K24" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="L24">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="M24">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="N24">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="O24" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="P24" t="s">
         <v>74</v>
       </c>
       <c r="Q24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -2026,85 +1993,85 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>156</v>
+      </c>
+      <c r="C25" t="s">
+        <v>157</v>
+      </c>
+      <c r="D25" t="s">
+        <v>158</v>
+      </c>
+      <c r="E25" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" t="s">
+        <v>70</v>
+      </c>
+      <c r="H25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I25" t="s">
+        <v>152</v>
+      </c>
+      <c r="J25" t="s">
+        <v>159</v>
+      </c>
+      <c r="K25" t="s">
+        <v>160</v>
+      </c>
+      <c r="L25">
+        <v>105</v>
+      </c>
+      <c r="M25">
+        <v>13</v>
+      </c>
+      <c r="N25">
+        <v>2.45</v>
+      </c>
+      <c r="O25" t="s">
+        <v>161</v>
+      </c>
+      <c r="P25" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q25">
+        <v>11</v>
+      </c>
+      <c r="R25">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>1.5</v>
+      </c>
+      <c r="U25">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>32</v>
       </c>
-      <c r="B25" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>160</v>
-      </c>
-      <c r="C26" t="s">
-        <v>161</v>
-      </c>
-      <c r="D26" t="s">
         <v>162</v>
-      </c>
-      <c r="E26" t="s">
-        <v>57</v>
-      </c>
-      <c r="F26" t="s">
-        <v>58</v>
-      </c>
-      <c r="G26" t="s">
-        <v>163</v>
-      </c>
-      <c r="H26" t="s">
-        <v>79</v>
-      </c>
-      <c r="I26" t="s">
-        <v>163</v>
-      </c>
-      <c r="J26" t="s">
-        <v>164</v>
-      </c>
-      <c r="K26" t="s">
-        <v>165</v>
-      </c>
-      <c r="L26">
-        <v>108</v>
-      </c>
-      <c r="M26">
-        <v>13</v>
-      </c>
-      <c r="N26">
-        <v>2.6</v>
-      </c>
-      <c r="O26" t="s">
-        <v>166</v>
-      </c>
-      <c r="P26" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q26">
-        <v>60</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>1.5</v>
-      </c>
-      <c r="U26">
-        <v>0.4</v>
       </c>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C27" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D27" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E27" t="s">
         <v>57</v>
@@ -2113,37 +2080,37 @@
         <v>58</v>
       </c>
       <c r="G27" t="s">
-        <v>59</v>
+        <v>166</v>
       </c>
       <c r="H27" t="s">
         <v>79</v>
       </c>
       <c r="I27" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J27" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="K27" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L27">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="M27">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N27">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="O27" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="P27" t="s">
         <v>74</v>
       </c>
       <c r="Q27">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -2158,118 +2125,121 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>170</v>
+      </c>
+      <c r="C28" t="s">
+        <v>171</v>
+      </c>
+      <c r="D28" t="s">
+        <v>172</v>
+      </c>
+      <c r="E28" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" t="s">
+        <v>58</v>
+      </c>
+      <c r="G28" t="s">
+        <v>59</v>
+      </c>
+      <c r="H28" t="s">
+        <v>79</v>
+      </c>
+      <c r="I28" t="s">
+        <v>166</v>
+      </c>
+      <c r="J28" t="s">
+        <v>173</v>
+      </c>
+      <c r="K28" t="s">
+        <v>174</v>
+      </c>
+      <c r="L28">
+        <v>128</v>
+      </c>
+      <c r="M28">
+        <v>12</v>
+      </c>
+      <c r="N28">
+        <v>2.35</v>
+      </c>
+      <c r="O28" t="s">
+        <v>175</v>
+      </c>
+      <c r="P28" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q28">
+        <v>61</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>1.5</v>
+      </c>
+      <c r="U28">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>32</v>
       </c>
-      <c r="B28" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>174</v>
-      </c>
-      <c r="C29" t="s">
-        <v>175</v>
-      </c>
-      <c r="D29" t="s">
         <v>176</v>
-      </c>
-      <c r="E29" t="s">
-        <v>177</v>
-      </c>
-      <c r="F29" t="s">
-        <v>178</v>
-      </c>
-      <c r="G29" t="s">
-        <v>178</v>
-      </c>
-      <c r="H29" t="s">
-        <v>178</v>
-      </c>
-      <c r="J29" t="s">
-        <v>179</v>
-      </c>
-      <c r="K29" t="s">
-        <v>180</v>
-      </c>
-      <c r="L29">
-        <v>40</v>
-      </c>
-      <c r="M29">
-        <v>8</v>
-      </c>
-      <c r="N29">
-        <v>2</v>
-      </c>
-      <c r="O29" t="s">
-        <v>181</v>
-      </c>
-      <c r="P29" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q29">
-        <v>1000</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <v>1.5</v>
-      </c>
-      <c r="U29">
-        <v>0.45</v>
       </c>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
+        <v>177</v>
+      </c>
+      <c r="C30" t="s">
+        <v>178</v>
+      </c>
+      <c r="D30" t="s">
+        <v>179</v>
+      </c>
+      <c r="E30" t="s">
+        <v>180</v>
+      </c>
+      <c r="F30" t="s">
+        <v>181</v>
+      </c>
+      <c r="G30" t="s">
+        <v>181</v>
+      </c>
+      <c r="H30" t="s">
+        <v>181</v>
+      </c>
+      <c r="J30" t="s">
         <v>182</v>
       </c>
-      <c r="C30" t="s">
+      <c r="K30" t="s">
         <v>183</v>
       </c>
-      <c r="D30" t="s">
+      <c r="L30">
+        <v>40</v>
+      </c>
+      <c r="M30">
+        <v>8</v>
+      </c>
+      <c r="N30">
+        <v>2</v>
+      </c>
+      <c r="O30" t="s">
         <v>184</v>
-      </c>
-      <c r="E30" t="s">
-        <v>177</v>
-      </c>
-      <c r="F30" t="s">
-        <v>178</v>
-      </c>
-      <c r="G30" t="s">
-        <v>178</v>
-      </c>
-      <c r="H30" t="s">
-        <v>178</v>
-      </c>
-      <c r="J30" t="s">
-        <v>185</v>
-      </c>
-      <c r="K30" t="s">
-        <v>186</v>
-      </c>
-      <c r="L30">
-        <v>35</v>
-      </c>
-      <c r="M30">
-        <v>6</v>
-      </c>
-      <c r="N30">
-        <v>2.2</v>
-      </c>
-      <c r="O30" t="s">
-        <v>187</v>
       </c>
       <c r="P30" t="s">
         <v>65</v>
       </c>
       <c r="Q30">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -2284,8 +2254,90 @@
         <v>0.45</v>
       </c>
     </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>185</v>
+      </c>
+      <c r="C31" t="s">
+        <v>186</v>
+      </c>
+      <c r="D31" t="s">
+        <v>187</v>
+      </c>
+      <c r="E31" t="s">
+        <v>180</v>
+      </c>
+      <c r="F31" t="s">
+        <v>181</v>
+      </c>
+      <c r="G31" t="s">
+        <v>181</v>
+      </c>
+      <c r="H31" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>188</v>
+      </c>
+      <c r="C32" t="s">
+        <v>189</v>
+      </c>
+      <c r="D32" t="s">
+        <v>190</v>
+      </c>
+      <c r="E32" t="s">
+        <v>180</v>
+      </c>
+      <c r="F32" t="s">
+        <v>181</v>
+      </c>
+      <c r="G32" t="s">
+        <v>181</v>
+      </c>
+      <c r="H32" t="s">
+        <v>181</v>
+      </c>
+      <c r="J32" t="s">
+        <v>191</v>
+      </c>
+      <c r="K32" t="s">
+        <v>192</v>
+      </c>
+      <c r="L32">
+        <v>35</v>
+      </c>
+      <c r="M32">
+        <v>6</v>
+      </c>
+      <c r="N32">
+        <v>2.2</v>
+      </c>
+      <c r="O32" t="s">
+        <v>193</v>
+      </c>
+      <c r="P32" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q32">
+        <v>1001</v>
+      </c>
+      <c r="R32">
+        <v>0</v>
+      </c>
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>1.5</v>
+      </c>
+      <c r="U32">
+        <v>0.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/config/Config/Data/人物&怪物.xlsx
+++ b/config/Config/Data/人物&怪物.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="220">
   <si>
     <t>##var</t>
   </si>
@@ -76,6 +76,12 @@
     <t>attack_interval</t>
   </si>
   <si>
+    <t>starter_selectable</t>
+  </si>
+  <si>
+    <t>unlock_conditions</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -109,6 +115,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>(list#sep=;),UnlockCondition</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -172,6 +181,12 @@
     <t>普攻间隔秒；越低攻速越快</t>
   </si>
   <si>
+    <t>可作出征初始</t>
+  </si>
+  <si>
+    <t>解锁条件 AND；type:p1:p2</t>
+  </si>
+  <si>
     <t>互联网</t>
   </si>
   <si>
@@ -199,10 +214,10 @@
     <t>Internet</t>
   </si>
   <si>
-    <t>role_player_avatar</t>
-  </si>
-  <si>
-    <t>role_player_battle</t>
+    <t>role_lixin_avatar</t>
+  </si>
+  <si>
+    <t>role_lixin_battle</t>
   </si>
   <si>
     <t>campus_courage|cs_lixin_gamble|cs_lixin_crunch</t>
@@ -211,6 +226,9 @@
     <t>false</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>CS_ayun</t>
   </si>
   <si>
@@ -232,12 +250,15 @@
     <t>role_ayun_battle</t>
   </si>
   <si>
-    <t>campus_courage|cs_ayun_overload|cs_ayun_gaoliao</t>
+    <t>campus_courage|cs_ayun_dantiao|cs_ayun_overload|cs_ayun_gaoliao</t>
   </si>
   <si>
     <t>true</t>
   </si>
   <si>
+    <t>chapter:2:0</t>
+  </si>
+  <si>
     <t>烟草</t>
   </si>
   <si>
@@ -265,6 +286,9 @@
     <t>bz_jihong_cost|bz_jihong_bonus</t>
   </si>
   <si>
+    <t>chapter:3:0;favor:8:0</t>
+  </si>
+  <si>
     <t>体制编制</t>
   </si>
   <si>
@@ -295,6 +319,9 @@
     <t>gwy_wang_aura</t>
   </si>
   <si>
+    <t>chapter:5:0;renown:10:0</t>
+  </si>
+  <si>
     <t>银行</t>
   </si>
   <si>
@@ -319,6 +346,9 @@
     <t>yh_hangu_flow|yh_hangu_extend</t>
   </si>
   <si>
+    <t>grade:4:1;train:20:0</t>
+  </si>
+  <si>
     <t>土木类</t>
   </si>
   <si>
@@ -343,6 +373,9 @@
     <t>tm_yugu_smash</t>
   </si>
   <si>
+    <t>chapter:4:0</t>
+  </si>
+  <si>
     <t>TM_junjun</t>
   </si>
   <si>
@@ -361,6 +394,9 @@
     <t>tm_junjun_inspect</t>
   </si>
   <si>
+    <t>chapter:4:0;bond:2:1</t>
+  </si>
+  <si>
     <t>TM_PaoPao</t>
   </si>
   <si>
@@ -370,6 +406,18 @@
     <t>土木圣体，搞钱大师，商务经理</t>
   </si>
   <si>
+    <t>role_paopao_avatar</t>
+  </si>
+  <si>
+    <t>role_paopao_battle</t>
+  </si>
+  <si>
+    <t>tm_paopao_bargain</t>
+  </si>
+  <si>
+    <t>chapter:3:0</t>
+  </si>
+  <si>
     <t>TM_wantao</t>
   </si>
   <si>
@@ -388,6 +436,9 @@
     <t>tm_wantao_approve</t>
   </si>
   <si>
+    <t>chapter:5:0;kill:200:0</t>
+  </si>
+  <si>
     <t>医疗</t>
   </si>
   <si>
@@ -412,6 +463,9 @@
     <t>dr_chen_heal</t>
   </si>
   <si>
+    <t>archive:3:0</t>
+  </si>
+  <si>
     <t>Dr_xiao</t>
   </si>
   <si>
@@ -430,6 +484,9 @@
     <t>dr_xiao_ortho|dr_xiao_drunk</t>
   </si>
   <si>
+    <t>chapter:4:0;favor:12:0</t>
+  </si>
+  <si>
     <t>机械</t>
   </si>
   <si>
@@ -457,6 +514,9 @@
     <t>xiebo_dismantle|xiebo_patch|xiebo_torque</t>
   </si>
   <si>
+    <t>grade:4:3;train:40:0</t>
+  </si>
+  <si>
     <t>能源</t>
   </si>
   <si>
@@ -499,6 +559,9 @@
     <t>wuzi_boost|wuzi_grid</t>
   </si>
   <si>
+    <t>chapter:5:0;bond:9:1</t>
+  </si>
+  <si>
     <t>创业</t>
   </si>
   <si>
@@ -523,6 +586,9 @@
     <t>bus_laizhen_mobilize</t>
   </si>
   <si>
+    <t>chapter:5:0;renown:15:0</t>
+  </si>
+  <si>
     <t>Bus_longtou</t>
   </si>
   <si>
@@ -541,6 +607,9 @@
     <t>bus_longtou_turnaround</t>
   </si>
   <si>
+    <t>chapter:5:0;kill:300:0;train:50:0</t>
+  </si>
+  <si>
     <t>其他召唤单位</t>
   </si>
   <si>
@@ -575,6 +644,15 @@
   </si>
   <si>
     <t>仁心老陈有事，就是他们有事，真上。</t>
+  </si>
+  <si>
+    <t>role_tempcitizen_avatar</t>
+  </si>
+  <si>
+    <t>role_tempcitizen_battle</t>
+  </si>
+  <si>
+    <t>mow_old_help</t>
   </si>
   <si>
     <t>temp_hire</t>
@@ -969,7 +1047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:AD32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13.571428571428571" customWidth="1"/>
@@ -979,7 +1057,7 @@
     <col min="5" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1043,175 +1121,193 @@
       <c r="U1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J2" t="s">
         <v>24</v>
       </c>
-      <c r="G2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
-      </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R2" t="s">
         <v>30</v>
       </c>
-      <c r="Q2" t="s">
-        <v>31</v>
-      </c>
-      <c r="R2" t="s">
-        <v>28</v>
-      </c>
       <c r="S2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="T2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="U2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="V2" t="s">
+        <v>32</v>
+      </c>
+      <c r="W2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="N3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="P3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Q3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="R3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="S3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="T3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="U3" t="s">
-        <v>52</v>
+        <v>55</v>
+      </c>
+      <c r="V3" t="s">
+        <v>56</v>
+      </c>
+      <c r="W3" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H5" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I5" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="L5">
         <v>110</v>
@@ -1223,10 +1319,10 @@
         <v>2.7</v>
       </c>
       <c r="O5" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="P5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1243,37 +1339,43 @@
       <c r="U5">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6" t="s">
+        <v>65</v>
+      </c>
+      <c r="I6" t="s">
         <v>66</v>
       </c>
-      <c r="C6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F6" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" t="s">
-        <v>70</v>
-      </c>
-      <c r="H6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I6" t="s">
-        <v>61</v>
-      </c>
       <c r="J6" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="L6">
         <v>95</v>
@@ -1285,10 +1387,10 @@
         <v>2.6</v>
       </c>
       <c r="O6" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="P6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q6">
         <v>5</v>
@@ -1305,45 +1407,51 @@
       <c r="U6">
         <v>0.4</v>
       </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
+      <c r="G8" t="s">
         <v>76</v>
       </c>
-      <c r="C8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" t="s">
-        <v>70</v>
-      </c>
       <c r="H8" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I8" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J8" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="K8" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="L8">
         <v>130</v>
@@ -1355,10 +1463,10 @@
         <v>2.2</v>
       </c>
       <c r="O8" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="P8" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q8">
         <v>15</v>
@@ -1375,45 +1483,51 @@
       <c r="U8">
         <v>0.4</v>
       </c>
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="W8" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G10" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="H10" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I10" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="J10" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="K10" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>125</v>
@@ -1425,10 +1539,10 @@
         <v>2.2</v>
       </c>
       <c r="O10" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="P10" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q10">
         <v>20</v>
@@ -1445,45 +1559,51 @@
       <c r="U10">
         <v>0.4</v>
       </c>
+      <c r="V10" t="b">
+        <v>1</v>
+      </c>
+      <c r="W10" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G12" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H12" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I12" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="J12" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="K12" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="L12">
         <v>150</v>
@@ -1495,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="O12" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="P12" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q12">
         <v>25</v>
@@ -1515,45 +1635,51 @@
       <c r="U12">
         <v>0.4</v>
       </c>
+      <c r="V12" t="b">
+        <v>1</v>
+      </c>
+      <c r="W12" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="14" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G14" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H14" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I14" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="J14" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="K14" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="L14">
         <v>150</v>
@@ -1565,10 +1691,10 @@
         <v>1.9</v>
       </c>
       <c r="O14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="P14" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q14">
         <v>40</v>
@@ -1585,37 +1711,43 @@
       <c r="U14">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V14" t="b">
+        <v>1</v>
+      </c>
+      <c r="W14" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="D15" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G15" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H15" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I15" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="J15" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="K15" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="L15">
         <v>142</v>
@@ -1627,10 +1759,10 @@
         <v>2.25</v>
       </c>
       <c r="O15" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="P15" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q15">
         <v>42</v>
@@ -1647,48 +1779,111 @@
       <c r="U15">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="V15" t="b">
+        <v>1</v>
+      </c>
+      <c r="W15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
+        <v>128</v>
+      </c>
+      <c r="C16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D16" t="s">
+        <v>130</v>
+      </c>
+      <c r="E16" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" t="s">
+        <v>65</v>
+      </c>
+      <c r="I16" t="s">
         <v>116</v>
       </c>
-      <c r="C16" t="s">
-        <v>117</v>
-      </c>
-      <c r="D16" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="J16" t="s">
+        <v>131</v>
+      </c>
+      <c r="K16" t="s">
+        <v>132</v>
+      </c>
+      <c r="L16">
+        <v>128</v>
+      </c>
+      <c r="M16">
+        <v>12.5</v>
+      </c>
+      <c r="N16">
+        <v>2.4</v>
+      </c>
+      <c r="O16" t="s">
+        <v>133</v>
+      </c>
+      <c r="P16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>43</v>
+      </c>
+      <c r="R16">
+        <v>6</v>
+      </c>
+      <c r="S16">
+        <v>0.05</v>
+      </c>
+      <c r="T16">
+        <v>1.5</v>
+      </c>
+      <c r="U16">
+        <v>0.4</v>
+      </c>
+      <c r="V16" t="b">
+        <v>1</v>
+      </c>
+      <c r="W16" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="E17" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G17" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H17" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I17" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="J17" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="K17" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="L17">
         <v>135</v>
@@ -1700,10 +1895,10 @@
         <v>2.35</v>
       </c>
       <c r="O17" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="P17" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q17">
         <v>41</v>
@@ -1720,45 +1915,51 @@
       <c r="U17">
         <v>0.4</v>
       </c>
+      <c r="V17" t="b">
+        <v>1</v>
+      </c>
+      <c r="W17" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C19" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="D19" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="E19" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G19" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H19" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I19" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="J19" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="K19" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -1770,10 +1971,10 @@
         <v>2.5</v>
       </c>
       <c r="O19" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="P19" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q19">
         <v>30</v>
@@ -1790,37 +1991,43 @@
       <c r="U19">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W19" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="C20" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="D20" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="E20" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F20" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G20" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H20" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I20" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="J20" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="K20" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="L20">
         <v>105</v>
@@ -1832,10 +2039,10 @@
         <v>2.45</v>
       </c>
       <c r="O20" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="P20" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q20">
         <v>50</v>
@@ -1852,45 +2059,51 @@
       <c r="U20">
         <v>0.4</v>
       </c>
+      <c r="V20" t="b">
+        <v>1</v>
+      </c>
+      <c r="W20" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="22" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="C22" t="s">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="D22" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="E22" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F22" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="G22" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H22" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I22" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="J22" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="K22" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="L22">
         <v>95</v>
@@ -1902,10 +2115,10 @@
         <v>2.4</v>
       </c>
       <c r="O22" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="P22" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q22">
         <v>10</v>
@@ -1922,45 +2135,51 @@
       <c r="U22">
         <v>0.4</v>
       </c>
+      <c r="V22" t="b">
+        <v>1</v>
+      </c>
+      <c r="W22" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="24" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="C24" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="D24" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="E24" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F24" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G24" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H24" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I24" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="J24" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="K24" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="L24">
         <v>145</v>
@@ -1972,10 +2191,10 @@
         <v>2.15</v>
       </c>
       <c r="O24" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="P24" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q24">
         <v>12</v>
@@ -1992,37 +2211,43 @@
       <c r="U24">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V24" t="b">
+        <v>1</v>
+      </c>
+      <c r="W24" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="C25" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="D25" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="E25" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F25" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H25" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I25" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="J25" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="K25" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="L25">
         <v>105</v>
@@ -2034,10 +2259,10 @@
         <v>2.45</v>
       </c>
       <c r="O25" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="P25" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q25">
         <v>11</v>
@@ -2054,45 +2279,51 @@
       <c r="U25">
         <v>0.4</v>
       </c>
+      <c r="V25" t="b">
+        <v>1</v>
+      </c>
+      <c r="W25" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="C27" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="D27" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="E27" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F27" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G27" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="H27" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I27" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="J27" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="K27" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="L27">
         <v>108</v>
@@ -2104,10 +2335,10 @@
         <v>2.6</v>
       </c>
       <c r="O27" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="P27" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q27">
         <v>60</v>
@@ -2124,37 +2355,43 @@
       <c r="U27">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="V27" t="b">
+        <v>1</v>
+      </c>
+      <c r="W27" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="28" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="C28" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="D28" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="E28" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F28" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G28" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H28" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I28" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="J28" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="K28" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="L28">
         <v>128</v>
@@ -2166,10 +2403,10 @@
         <v>2.35</v>
       </c>
       <c r="O28" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="P28" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="Q28">
         <v>61</v>
@@ -2186,42 +2423,48 @@
       <c r="U28">
         <v>0.4</v>
       </c>
+      <c r="V28" t="b">
+        <v>1</v>
+      </c>
+      <c r="W28" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="30" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="C30" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="D30" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="E30" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="F30" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="G30" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="H30" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="J30" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="K30" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="L30">
         <v>40</v>
@@ -2233,10 +2476,10 @@
         <v>2</v>
       </c>
       <c r="O30" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="P30" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="Q30">
         <v>1000</v>
@@ -2253,57 +2496,108 @@
       <c r="U30">
         <v>0.45</v>
       </c>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="V30" t="b">
+        <v>0</v>
+      </c>
+      <c r="W30" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="C31" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="D31" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="E31" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="F31" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="G31" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="H31" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+      <c r="I31" t="s">
+        <v>71</v>
+      </c>
+      <c r="J31" t="s">
+        <v>211</v>
+      </c>
+      <c r="K31" t="s">
+        <v>212</v>
+      </c>
+      <c r="L31">
+        <v>42</v>
+      </c>
+      <c r="M31">
+        <v>5</v>
+      </c>
+      <c r="N31">
+        <v>2</v>
+      </c>
+      <c r="O31" t="s">
+        <v>213</v>
+      </c>
+      <c r="P31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q31">
+        <v>1002</v>
+      </c>
+      <c r="R31">
+        <v>0</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>1.5</v>
+      </c>
+      <c r="U31">
+        <v>0.5</v>
+      </c>
+      <c r="V31" t="b">
+        <v>0</v>
+      </c>
+      <c r="W31" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="C32" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="D32" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="E32" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="F32" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="G32" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="H32" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="J32" t="s">
-        <v>191</v>
+        <v>217</v>
       </c>
       <c r="K32" t="s">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="L32">
         <v>35</v>
@@ -2315,10 +2609,10 @@
         <v>2.2</v>
       </c>
       <c r="O32" t="s">
-        <v>193</v>
+        <v>219</v>
       </c>
       <c r="P32" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="Q32">
         <v>1001</v>
@@ -2335,9 +2629,15 @@
       <c r="U32">
         <v>0.45</v>
       </c>
+      <c r="V32" t="b">
+        <v>0</v>
+      </c>
+      <c r="W32" t="s">
+        <v>71</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>